--- a/artfynd/A 352-2026 artfynd.xlsx
+++ b/artfynd/A 352-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>95698405</v>
       </c>
       <c r="B2" t="n">
-        <v>42702</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43426</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -731,10 +726,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>513223.195828756</v>
+        <v>513223</v>
       </c>
       <c r="R2" t="n">
-        <v>6745610.631052817</v>
+        <v>6745611</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -800,6 +795,259 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>95698701</v>
+      </c>
+      <c r="B3" t="n">
+        <v>43426</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100942</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Väddnätfjäril</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Euphydryas aurinia</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Rottemburg, 1775)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>N. Rågsvedsmyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>513209</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6745651</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2021-08-25</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>08:52</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2021-08-25</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>08:52</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Jonas Eriksson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Jonas Eriksson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>102938401</v>
+      </c>
+      <c r="B4" t="n">
+        <v>43426</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100942</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Väddnätfjäril</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Euphydryas aurinia</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Rottemburg, 1775)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>N. Rågsvedsmyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>513226</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6745649</v>
+      </c>
+      <c r="S4" t="n">
+        <v>6</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2022-08-17</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>11:06</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2022-08-17</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>11:06</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Totalt 5 kolonier på Norra Rågsvedsmyren. Utbildningsinventering tillsammans med Tobias Ekendahl.</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Uno Skog</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Uno Skog, Tobias Ekendahl</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 352-2026 artfynd.xlsx
+++ b/artfynd/A 352-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -795,6 +800,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95698405</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -918,6 +928,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95698701</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1048,8 +1063,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102938401</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>